--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:27</t>
+          <t>2026-08-25 10:25:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:28</t>
+          <t>2026-08-25 10:25:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:29</t>
+          <t>2026-08-25 10:25:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14410</v>
+        <v>14285</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.02%260,000</t>
+          <t>8.77%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.02%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.47%1,306,000</t>
+          <t>7.40%1,306,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.47%</t>
+          <t>7.40%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2855</v>
+        <v>2950</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.88%1,001,000</t>
+          <t>6.97%1,001,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1075</v>
+        <v>1095</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5430</v>
+        <v>5595</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.08%465,000</t>
+          <t>6.14%465,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2050</v>
+        <v>2075</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.73%1,161,000</t>
+          <t>5.69%1,161,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2070</v>
+        <v>2030</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.35%1,074,000</t>
+          <t>5.15%1,074,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.15%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1145</v>
+        <v>1215</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.49%1,630,000</t>
+          <t>4.67%1,630,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>4.67%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5385</v>
+        <v>5720</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.45%343,000</t>
+          <t>4.63%343,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5565</v>
+        <v>5600</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.59%268,000</t>
+          <t>3.54%268,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.34%586</t>
+          <t>+1.37%594</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.15%2,231,000</t>
+          <t>3.13%2,231,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%175.5</t>
+          <t>+1.71%178.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>175.5</v>
+        <v>178.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.06%7,245,000</t>
+          <t>3.05%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.02%107.5</t>
+          <t>+1.4%109</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>107.5</v>
+        <v>109</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.82%10,877,000</t>
+          <t>2.80%10,877,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>+9.96%419.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1735</v>
+        <v>419.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.64%632,000</t>
+          <t>2.73%2,753,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>632000</v>
+        <v>2753000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:13</t>
+          <t>2026-08-25 17:37:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.03%381.5</t>
+          <t>+3.99%404</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>381.5</v>
+        <v>404</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.53%2,753,000</t>
+          <t>2.56%2,682,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2753000</v>
+        <v>2682000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.14%388.5</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>388.5</v>
+        <v>1710</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.51%2,682,000</t>
+          <t>2.55%632,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2682000</v>
+        <v>632000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>+4.72%188.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+4.72%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3765</v>
+        <v>188.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.41%266,000</t>
+          <t>2.42%5,445,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>266000</v>
+        <v>5445000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.25%180</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>180</v>
+        <v>3735</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.36%5,445,000</t>
+          <t>2.35%266,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5445000</v>
+        <v>266000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.2%5365</t>
+          <t>+3.82%5570</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.82%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5365</v>
+        <v>5570</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.12%164,000</t>
+          <t>2.16%164,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.95%3735</t>
+          <t>+3.48%3865</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+3.48%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3735</v>
+        <v>3865</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.93%215,000</t>
+          <t>1.96%215,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.1%794</t>
+          <t>+5.16%835</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+5.16%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.61%844,013</t>
+          <t>1.66%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6300</v>
+        <v>6440</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>435.5</v>
+        <v>444</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.02%716,000</t>
+          <t>1.00%716,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1135</v>
+        <v>1160</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.52%758</t>
+          <t>+9.84%530</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>758</v>
+        <v>530</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.46%250,000</t>
+          <t>0.47%373,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>250000</v>
+        <v>373000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.96%287</t>
+          <t>+3.14%296</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.22%923</t>
+          <t>+1.32%768</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>923</v>
+        <v>768</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.44%196,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>196000</v>
+        <v>250000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.95%482.5</t>
+          <t>+7.05%2960</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.95%</t>
+          <t>+7.05%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>482.5</v>
+        <v>2960</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.43%373,000</t>
+          <t>0.44%63,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>373000</v>
+        <v>63000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:14</t>
+          <t>2026-08-25 17:37:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.31%2765</t>
+          <t>+0.22%925</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2765</v>
+        <v>925</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.42%63,000</t>
+          <t>0.43%196,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>63000</v>
+        <v>196000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.44%341</t>
+          <t>+1.91%347.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>341</v>
+        <v>347.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.15%87.7</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>87.7</v>
+        <v>5205</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.41%1,957,000</t>
+          <t>0.41%33,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1957000</v>
+        <v>33000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>-0.23%87.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5155</v>
+        <v>87.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.41%33,000</t>
+          <t>0.40%1,957,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>33000</v>
+        <v>1957000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.63%643</t>
+          <t>+5.39%1270</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>643</v>
+        <v>1270</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.40%261,000</t>
+          <t>0.40%134,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>261000</v>
+        <v>134000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>+1.89%15400</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>15115</v>
+        <v>15400</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.47%1065</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1065</v>
+        <v>1485</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.40%155,000</t>
+          <t>0.40%113,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>155000</v>
+        <v>113000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>+0.47%1070</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1455</v>
+        <v>1070</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.39%155,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>113000</v>
+        <v>155000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.84%1205</t>
+          <t>-2.33%628</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1205</v>
+        <v>628</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.39%134,000</t>
+          <t>0.39%261,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>134000</v>
+        <v>261000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2070</v>
+        <v>1965</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.38%76,000</t>
+          <t>0.35%76,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.64%1570</t>
+          <t>-3.82%1510</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1570</v>
+        <v>1510</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.37%98,000</t>
+          <t>0.35%98,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:16</t>
+          <t>2026-08-25 17:37:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.33%151</t>
+          <t>-0.33%150.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2958,16 +2958,16 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>151</v>
+        <v>150.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.23%629,000</t>
+          <t>0.22%629,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K42" t="n">

--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:49</t>
+          <t>2026-08-25 19:52:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:50</t>
+          <t>2026-08-25 19:52:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:51</t>
+          <t>2026-08-25 19:52:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:38</t>
+          <t>2026-08-25 21:10:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:39</t>
+          <t>2026-08-25 21:10:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:40</t>
+          <t>2026-08-25 21:10:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:10</t>
+          <t>2026-08-25 21:29:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:11</t>
+          <t>2026-08-25 21:29:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:12</t>
+          <t>2026-08-25 21:29:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:34</t>
+          <t>2026-08-25 21:32:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:36</t>
+          <t>2026-08-25 21:32:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:37</t>
+          <t>2026-08-25 21:32:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:08</t>
+          <t>2026-08-25 22:04:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:09</t>
+          <t>2026-08-25 22:04:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:11</t>
+          <t>2026-08-25 22:04:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
